--- a/Figure 5/Figure 5-H.xlsx
+++ b/Figure 5/Figure 5-H.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7B90FA-7C3C-4F7A-A124-70EAFA4B5096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27259FB-721E-41C9-B27E-46AC1068B130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20140" yWindow="350" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,19 +93,7 @@
     <t>ETEC+WB800_KR32 5</t>
   </si>
   <si>
-    <r>
-      <t>NF-κ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>B</t>
-    </r>
+    <t>NF-κB</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -116,7 +104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +124,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,9 +146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -454,184 +436,185 @@
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>0.80764673326636749</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>1.1355112485342689</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1.156046632183815</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>1.2904277226878857</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>1.0221761212451803</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>0.73024825067940591</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>1.5316035238114851</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>2.0620878660521269</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2.1003180460043875</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>2.0897324560141035</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>2.6051850834582631</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>1.4304399179855136</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>1.7177859408242764</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>2.5198157532412431</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>2.7214611942558351</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>2.5661057734831889</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>2.5464227623570412</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>0.68862778500531374</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>1.7033009161130495</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>1.474831635990435</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>0.8315766895703951</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>1.7473425332793873</v>
       </c>
     </row>
